--- a/Pipeline-Feature Plan.xlsx
+++ b/Pipeline-Feature Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galha\Downloads\My Repositories\DS-principles-project\PRE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galha\Downloads\My Repositories\DS-principles-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CC00A0-B92B-42BA-9394-471C81D3FFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC0A120-8707-42C3-B839-5B0E03A9FBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D2E0F34-A641-40C1-8D7F-D8BA3B32531F}"/>
   </bookViews>
@@ -233,9 +233,6 @@
     <t>- added int: 'num_genres'</t>
   </si>
   <si>
-    <t>- added 20 bools for each genre (ex: 'Action')</t>
-  </si>
-  <si>
     <t>- added bool: 'top10_prod_comps'</t>
   </si>
   <si>
@@ -300,6 +297,9 @@
   </si>
   <si>
     <t>Leave as is</t>
+  </si>
+  <si>
+    <t>- added 19 bools for each genre (ex: 'Action')</t>
   </si>
 </sst>
 </file>
@@ -1076,6 +1076,7 @@
     <col min="4" max="4" width="40" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="38.85546875" customWidth="1"/>
     <col min="6" max="6" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" customWidth="1"/>
     <col min="9" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1241,10 +1242,10 @@
         <v>54</v>
       </c>
       <c r="E10" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="24" t="s">
         <v>85</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1261,10 +1262,10 @@
         <v>55</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1297,7 +1298,7 @@
         <v>55</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1314,7 +1315,7 @@
         <v>55</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1349,7 +1350,7 @@
         <v>64</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1366,10 +1367,10 @@
         <v>52</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1386,10 +1387,10 @@
         <v>52</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1406,10 +1407,10 @@
         <v>52</v>
       </c>
       <c r="E19" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="25" t="s">
         <v>70</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1498,7 +1499,7 @@
     </row>
     <row r="30" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="B30" s="31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E30" s="6"/>
     </row>
@@ -1510,10 +1511,10 @@
         <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1524,10 +1525,10 @@
         <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,10 +1539,10 @@
         <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1552,10 +1553,10 @@
         <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1563,13 +1564,13 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1580,10 +1581,10 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1594,10 +1595,10 @@
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1608,10 +1609,10 @@
         <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1622,10 +1623,10 @@
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1636,10 +1637,10 @@
         <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1650,10 +1651,10 @@
         <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
